--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-practitionerrole-smartcard.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-practitionerrole-smartcard.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="184">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,13 +250,10 @@
 </t>
   </si>
   <si>
-    <t>CarteProfessionnel</t>
-  </si>
-  <si>
     <t>Données descriptives du moyen d’identification des personnes physiques via une carte de professionnel.</t>
   </si>
   <si>
-    <t>La carte est rattachée à l’exercice d’une profession donnée et non au professionnel lui-même, un professionnel exerçant simultanément deux professions a deux cartes.</t>
+    <t>Synonyme : CarteProfessionnel ; la carte est rattachée à l’exercice d’une profession donnée et non au professionnel lui-même, un professionnel exerçant simultanément deux professions a deux cartes.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -331,12 +328,15 @@
     <t>type</t>
   </si>
   <si>
-    <t>typeCarte</t>
-  </si>
-  <si>
     <t>Type de carte de professionnel (CPx)</t>
   </si>
   <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Synonyme : typeCarte</t>
+  </si>
+  <si>
     <t>Extension.extension:type.id</t>
   </si>
   <si>
@@ -347,9 +347,6 @@
   </si>
   <si>
     <t>Extension.extension.extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>Extension.extension:type.url</t>
@@ -422,12 +419,12 @@
     <t>number</t>
   </si>
   <si>
-    <t>numeroCarte</t>
-  </si>
-  <si>
     <t>Numéro de carte du professionnel.</t>
   </si>
   <si>
+    <t>Synonyme : numeroCarte</t>
+  </si>
+  <si>
     <t>Extension.extension:number.id</t>
   </si>
   <si>
@@ -444,9 +441,6 @@
   </si>
   <si>
     <t>period</t>
-  </si>
-  <si>
-    <t>periodValidite</t>
   </si>
   <si>
     <t>Période de validité de la carte.</t>
@@ -499,13 +493,13 @@
 </t>
   </si>
   <si>
-    <t>dateDebutValidite</t>
-  </si>
-  <si>
-    <t>Date de début de validité de la carte</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+    <t>Date de début de validité de la carte.</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>Synonyme : dateDebutValidite</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -524,13 +518,13 @@
     <t>Extension.extension.value[x].end</t>
   </si>
   <si>
-    <t>dateFinValidite</t>
-  </si>
-  <si>
-    <t>Date de fin de validité de la carte</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+    <t>Date de fin de validité de la carte.</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>Synonyme : dateFinValidite</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -548,13 +542,10 @@
     <t>cancellationDate</t>
   </si>
   <si>
-    <t>dateOpposition</t>
-  </si>
-  <si>
     <t>Date de mise en opposition de la carte.</t>
   </si>
   <si>
-    <t>Cette opposition implique la révocation des certifications embarquées dans la carte.</t>
+    <t>Synonyme : dateOpposition ; une opposition implique la révocation des certifications embarquées dans la carte.</t>
   </si>
   <si>
     <t>Extension.extension:cancellationDate.id</t>
@@ -585,10 +576,6 @@
   </si>
   <si>
     <t>Extension.extension:date.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta
-</t>
   </si>
   <si>
     <t>base64Binary
@@ -1082,10 +1069,10 @@
         <v>78</v>
       </c>
       <c r="M2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1144,7 +1131,7 @@
         <v>76</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
         <v>74</v>
@@ -1155,10 +1142,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1169,25 +1156,25 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1238,34 +1225,34 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1284,16 +1271,16 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1331,19 +1318,19 @@
         <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1352,24 +1339,24 @@
         <v>76</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>74</v>
@@ -1379,7 +1366,7 @@
         <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>74</v>
@@ -1391,15 +1378,17 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -1448,7 +1437,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1457,10 +1446,10 @@
         <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1482,25 +1471,25 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1551,22 +1540,22 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -1597,13 +1586,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1642,19 +1631,19 @@
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1663,10 +1652,10 @@
         <v>76</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>74</v>
@@ -1674,10 +1663,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1685,10 +1674,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1700,16 +1689,16 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1717,7 +1706,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>74</v>
@@ -1759,13 +1748,13 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>74</v>
@@ -1774,15 +1763,15 @@
         <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1793,7 +1782,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1805,13 +1794,13 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1850,43 +1839,43 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AF9" t="s" s="2">
+      <c r="AG9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1896,7 +1885,7 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
@@ -1908,13 +1897,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1941,11 +1930,11 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y10" s="2"/>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1963,33 +1952,33 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>74</v>
@@ -1999,7 +1988,7 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -2011,15 +2000,17 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2068,7 +2059,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2077,10 +2068,10 @@
         <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>74</v>
@@ -2088,7 +2079,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>106</v>
@@ -2102,25 +2093,25 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2171,27 +2162,27 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>108</v>
@@ -2217,13 +2208,13 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2262,19 +2253,19 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC13" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC13" t="s" s="2">
+      <c r="AD13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE13" t="s" s="2">
+      <c r="AF13" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2283,10 +2274,10 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>74</v>
@@ -2294,10 +2285,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2305,10 +2296,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2320,16 +2311,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2337,7 +2328,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -2379,13 +2370,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
@@ -2394,15 +2385,15 @@
         <v>74</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2413,25 +2404,25 @@
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="L15" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2482,33 +2473,33 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>74</v>
@@ -2518,7 +2509,7 @@
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2530,13 +2521,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2587,7 +2578,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2596,10 +2587,10 @@
         <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>74</v>
@@ -2607,7 +2598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>106</v>
@@ -2621,25 +2612,25 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2690,27 +2681,27 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>108</v>
@@ -2736,13 +2727,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2781,19 +2772,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2802,10 +2793,10 @@
         <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2813,10 +2804,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2824,10 +2815,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2839,16 +2830,16 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2856,7 +2847,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -2898,13 +2889,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2913,15 +2904,15 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2932,7 +2923,7 @@
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2944,13 +2935,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2989,43 +2980,43 @@
         <v>74</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AG20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>74</v>
@@ -3035,7 +3026,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -3047,13 +3038,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3104,30 +3095,30 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK21" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3138,25 +3129,25 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K22" t="s" s="2">
+      <c r="L22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3207,34 +3198,34 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3253,16 +3244,16 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3300,19 +3291,19 @@
         <v>74</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC23" t="s" s="2">
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE23" t="s" s="2">
+      <c r="AF23" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3321,21 +3312,21 @@
         <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3346,7 +3337,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3355,19 +3346,19 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3417,30 +3408,30 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3451,7 +3442,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3460,97 +3451,97 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="R25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>74</v>
@@ -3560,7 +3551,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3572,16 +3563,16 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3631,7 +3622,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3640,10 +3631,10 @@
         <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>74</v>
@@ -3651,7 +3642,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>106</v>
@@ -3665,25 +3656,25 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
+      <c r="L27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3734,27 +3725,27 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>108</v>
@@ -3780,13 +3771,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3825,19 +3816,19 @@
         <v>74</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC28" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC28" t="s" s="2">
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE28" t="s" s="2">
+      <c r="AF28" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3846,10 +3837,10 @@
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>74</v>
@@ -3857,10 +3848,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3868,10 +3859,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3883,16 +3874,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3900,7 +3891,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>74</v>
@@ -3942,13 +3933,13 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
@@ -3957,15 +3948,15 @@
         <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3976,7 +3967,7 @@
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -3988,13 +3979,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4045,33 +4036,33 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>74</v>
@@ -4093,13 +4084,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4150,7 +4141,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4159,10 +4150,10 @@
         <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>74</v>
@@ -4170,7 +4161,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>106</v>
@@ -4184,25 +4175,25 @@
         <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K32" t="s" s="2">
+      <c r="L32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4253,41 +4244,41 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>108</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -4299,15 +4290,17 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>28</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>74</v>
@@ -4344,19 +4337,19 @@
         <v>74</v>
       </c>
       <c r="AB33" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC33" t="s" s="2">
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
+      <c r="AF33" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4365,21 +4358,21 @@
         <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4387,10 +4380,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>74</v>
@@ -4402,16 +4395,16 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4419,7 +4412,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>74</v>
@@ -4461,13 +4454,13 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>74</v>
@@ -4476,15 +4469,15 @@
         <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4495,7 +4488,7 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4507,13 +4500,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4564,30 +4557,30 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4595,10 +4588,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4610,16 +4603,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4669,13 +4662,13 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>74</v>
@@ -4684,15 +4677,15 @@
         <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4715,13 +4708,13 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4772,22 +4765,22 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
